--- a/output/pdf_financials_xlsx/COPR.xlsx
+++ b/output/pdf_financials_xlsx/COPR.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8.332463000000001</v>
+        <v>-8.332463000000001</v>
       </c>
     </row>
     <row r="17">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8.332463000000001</v>
+        <v>-8.332463000000001</v>
       </c>
     </row>
     <row r="21">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>8.332463000000001</v>
+        <v>-8.332463000000001</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>106.4435</v>
+        <v>-106.4435</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>128.4168</v>
+        <v>-128.4168</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>122.367267</v>
+        <v>-122.367267</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>152.8321</v>
+        <v>-152.8321</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>166.64926</v>
+        <v>-166.64926</v>
       </c>
     </row>
     <row r="27">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8.332463000000001</v>
+        <v>-8.332463000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8.343799000000001</v>
+        <v>-8.321127000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.149637</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -4701,7 +4701,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -8152,10 +8156,10 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>8.332463000000001</v>
+        <v>-8.332463000000001</v>
       </c>
     </row>
     <row r="119">
@@ -8224,16 +8228,16 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>3.468943</v>
+        <v>-3.468943</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>3.794239</v>
+        <v>-3.794239</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>8.655624</v>
+        <v>-8.655624</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>8.629690999999999</v>
+        <v>-8.629690999999999</v>
       </c>
     </row>
     <row r="121">
@@ -8589,13 +8593,13 @@
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>3.671018</v>
+        <v>-3.671018</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>9.169926</v>
+        <v>-9.169926</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -8674,10 +8678,10 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>3.794239</v>
+        <v>-3.794239</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>8.655624</v>
+        <v>-8.655624</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -9185,10 +9189,10 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3.193305</v>
+        <v>-3.193305</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>3.852504</v>
+        <v>-3.852504</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -9267,10 +9271,10 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3.189527</v>
+        <v>-3.189527</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>3.468943</v>
+        <v>-3.468943</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/COPR.xlsx
+++ b/output/pdf_financials_xlsx/COPR.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025964</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.373196</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.212185</v>
       </c>
     </row>
     <row r="13">
@@ -1025,13 +1025,13 @@
         <v>-3.852504</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.671018</v>
+        <v>-3.645054</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-9.169926</v>
+        <v>-8.79673</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.332463000000001</v>
+        <v>-8.120278000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1069,13 +1069,13 @@
         <v>-3.852504</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.671018</v>
+        <v>-3.645054</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-9.169926</v>
+        <v>-8.79673</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.321127000000001</v>
+        <v>-8.108942000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.965269</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.300862</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.170801</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.225074</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.892441</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.965269</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.300862</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.170801</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.225074</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.892441</v>
       </c>
     </row>
     <row r="37">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.477937</v>
+        <v>0.512668</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.5142060000000001</v>
+        <v>0.213344</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.465437</v>
+        <v>0.294636</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.976038</v>
+        <v>0.750964</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.429415</v>
+        <v>0.536974</v>
       </c>
     </row>
     <row r="49">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">

--- a/output/pdf_financials_xlsx/COPR.xlsx
+++ b/output/pdf_financials_xlsx/COPR.xlsx
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.068644</v>
       </c>
     </row>
     <row r="112">
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.001168</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.068644</v>
       </c>
     </row>
     <row r="135">
@@ -3431,7 +3431,7 @@
         <v>-8.598951</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-8.215966999999999</v>
+        <v>-8.284611</v>
       </c>
     </row>
   </sheetData>
@@ -5755,7 +5755,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -7328,7 +7332,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
